--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/pre LAM_HRM-2031-0380/Panel 7/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/pre LAM_HRM-2031-0380/Panel 7/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.84539</v>
+        <v>16.86421</v>
       </c>
       <c r="D2" t="n">
-        <v>16.57036</v>
+        <v>16.57367</v>
       </c>
       <c r="E2" t="n">
-        <v>16.79254</v>
+        <v>16.74652</v>
       </c>
       <c r="F2" t="n">
-        <v>43.008</v>
+        <v>43.27894</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05139</v>
+        <v>0.05104</v>
       </c>
       <c r="H2" t="n">
-        <v>1.83928</v>
+        <v>1.80865</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.89895</v>
+        <v>16.8168</v>
       </c>
       <c r="D3" t="n">
-        <v>16.61939</v>
+        <v>16.30008</v>
       </c>
       <c r="E3" t="n">
-        <v>16.15615</v>
+        <v>16.67615</v>
       </c>
       <c r="F3" t="n">
-        <v>43.37242</v>
+        <v>42.4497</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05138</v>
+        <v>0.05068</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8264</v>
+        <v>1.80656</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.57606</v>
+        <v>16.81889</v>
       </c>
       <c r="D4" t="n">
-        <v>16.2573</v>
+        <v>16.45521</v>
       </c>
       <c r="E4" t="n">
-        <v>16.64748</v>
+        <v>16.74542</v>
       </c>
       <c r="F4" t="n">
-        <v>43.03319</v>
+        <v>42.38824</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05009</v>
+        <v>0.05048</v>
       </c>
       <c r="H4" t="n">
-        <v>1.81534</v>
+        <v>1.82525</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.33656</v>
+        <v>17.17154</v>
       </c>
       <c r="D5" t="n">
-        <v>16.33984</v>
+        <v>16.57535</v>
       </c>
       <c r="E5" t="n">
-        <v>16.80468</v>
+        <v>16.8419</v>
       </c>
       <c r="F5" t="n">
-        <v>42.14481</v>
+        <v>42.47266</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05042</v>
+        <v>0.05038</v>
       </c>
       <c r="H5" t="n">
-        <v>1.78064</v>
+        <v>1.82424</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.79007</v>
+        <v>16.94068</v>
       </c>
       <c r="D6" t="n">
-        <v>16.77004</v>
+        <v>16.4601</v>
       </c>
       <c r="E6" t="n">
-        <v>16.59914</v>
+        <v>16.72229</v>
       </c>
       <c r="F6" t="n">
-        <v>42.69451</v>
+        <v>42.21859</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0497</v>
+        <v>0.05071</v>
       </c>
       <c r="H6" t="n">
-        <v>1.83961</v>
+        <v>1.82799</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.06748</v>
+        <v>17.00354</v>
       </c>
       <c r="D7" t="n">
-        <v>16.3028</v>
+        <v>16.47442</v>
       </c>
       <c r="E7" t="n">
-        <v>17.04084</v>
+        <v>16.65858</v>
       </c>
       <c r="F7" t="n">
-        <v>42.04481</v>
+        <v>41.87983</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05012</v>
+        <v>0.04986</v>
       </c>
       <c r="H7" t="n">
-        <v>1.83518</v>
+        <v>1.81512</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.75732</v>
+        <v>16.8121</v>
       </c>
       <c r="D8" t="n">
-        <v>16.87691</v>
+        <v>16.64619</v>
       </c>
       <c r="E8" t="n">
-        <v>16.73212</v>
+        <v>16.78307</v>
       </c>
       <c r="F8" t="n">
-        <v>42.80436</v>
+        <v>41.91227</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05033</v>
+        <v>0.05115</v>
       </c>
       <c r="H8" t="n">
-        <v>1.82089</v>
+        <v>1.79472</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.56507</v>
+        <v>17.06056</v>
       </c>
       <c r="D9" t="n">
-        <v>16.70947</v>
+        <v>16.39119</v>
       </c>
       <c r="E9" t="n">
-        <v>16.66459</v>
+        <v>16.78787</v>
       </c>
       <c r="F9" t="n">
-        <v>41.87676</v>
+        <v>42.86583</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05057</v>
+        <v>0.05001</v>
       </c>
       <c r="H9" t="n">
-        <v>1.80495</v>
+        <v>1.78404</v>
       </c>
     </row>
     <row r="10">
@@ -660,712 +660,744 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.76732</v>
+        <v>16.98542</v>
       </c>
       <c r="D10" t="n">
-        <v>16.52604</v>
+        <v>16.5659</v>
       </c>
       <c r="E10" t="n">
-        <v>16.71296</v>
+        <v>16.9152</v>
       </c>
       <c r="F10" t="n">
-        <v>42.31609</v>
+        <v>42.75684</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05093</v>
+        <v>0.05032</v>
       </c>
       <c r="H10" t="n">
-        <v>1.87031</v>
+        <v>1.8305</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Pad 2</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>16.8105</v>
-      </c>
-      <c r="D11" t="n">
-        <v>16.82146</v>
-      </c>
-      <c r="E11" t="n">
-        <v>16.33285</v>
-      </c>
-      <c r="F11" t="n">
-        <v>42.08817</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.05078</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.81427</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.43449</v>
+        <v>16.64934</v>
       </c>
       <c r="D12" t="n">
-        <v>16.70071</v>
+        <v>16.23366</v>
       </c>
       <c r="E12" t="n">
-        <v>16.6723</v>
+        <v>16.50342</v>
       </c>
       <c r="F12" t="n">
-        <v>41.85484</v>
+        <v>42.98624</v>
       </c>
       <c r="G12" t="n">
-        <v>0.04973</v>
+        <v>0.05026</v>
       </c>
       <c r="H12" t="n">
-        <v>1.81182</v>
+        <v>1.83288</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.54045</v>
+        <v>16.81925</v>
       </c>
       <c r="D13" t="n">
-        <v>16.23649</v>
+        <v>16.52819</v>
       </c>
       <c r="E13" t="n">
-        <v>16.30323</v>
+        <v>16.618</v>
       </c>
       <c r="F13" t="n">
-        <v>42.5252</v>
+        <v>42.87765</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05048</v>
+        <v>0.05094</v>
       </c>
       <c r="H13" t="n">
-        <v>1.83833</v>
+        <v>1.79217</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.61279</v>
+        <v>17.18042</v>
       </c>
       <c r="D14" t="n">
-        <v>16.66861</v>
+        <v>16.52768</v>
       </c>
       <c r="E14" t="n">
-        <v>16.52401</v>
+        <v>16.74717</v>
       </c>
       <c r="F14" t="n">
-        <v>42.31212</v>
+        <v>42.15249</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05081</v>
+        <v>0.05022</v>
       </c>
       <c r="H14" t="n">
-        <v>1.84629</v>
+        <v>1.79205</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.00974</v>
+        <v>16.67121</v>
       </c>
       <c r="D15" t="n">
-        <v>16.50064</v>
+        <v>16.54127</v>
       </c>
       <c r="E15" t="n">
-        <v>16.59835</v>
+        <v>16.63596</v>
       </c>
       <c r="F15" t="n">
-        <v>42.71493</v>
+        <v>42.28218</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05109</v>
+        <v>0.0503</v>
       </c>
       <c r="H15" t="n">
-        <v>1.81005</v>
+        <v>1.82869</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.93397</v>
+        <v>16.93735</v>
       </c>
       <c r="D16" t="n">
-        <v>16.4468</v>
+        <v>16.61232</v>
       </c>
       <c r="E16" t="n">
-        <v>16.9087</v>
+        <v>16.93613</v>
       </c>
       <c r="F16" t="n">
-        <v>42.30456</v>
+        <v>42.1646</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05137</v>
+        <v>0.05084</v>
       </c>
       <c r="H16" t="n">
-        <v>1.80268</v>
+        <v>1.83206</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.67914</v>
+        <v>16.92154</v>
       </c>
       <c r="D17" t="n">
-        <v>16.73334</v>
+        <v>16.46554</v>
       </c>
       <c r="E17" t="n">
-        <v>16.60665</v>
+        <v>16.76348</v>
       </c>
       <c r="F17" t="n">
-        <v>42.47559</v>
+        <v>42.92395</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0505</v>
+        <v>0.05151</v>
       </c>
       <c r="H17" t="n">
-        <v>1.86887</v>
+        <v>1.83488</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.83619</v>
+        <v>16.84242</v>
       </c>
       <c r="D18" t="n">
-        <v>16.73849</v>
+        <v>16.60664</v>
       </c>
       <c r="E18" t="n">
-        <v>16.57416</v>
+        <v>16.61289</v>
       </c>
       <c r="F18" t="n">
-        <v>42.4862</v>
+        <v>42.5685</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05001</v>
+        <v>0.05035</v>
       </c>
       <c r="H18" t="n">
-        <v>1.79402</v>
+        <v>1.81746</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>17.25041</v>
+      </c>
+      <c r="D19" t="n">
+        <v>16.74644</v>
+      </c>
+      <c r="E19" t="n">
+        <v>17.24922</v>
+      </c>
+      <c r="F19" t="n">
+        <v>41.94556</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.05047</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.83329</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>16.36879</v>
-      </c>
-      <c r="D19" t="n">
-        <v>16.60997</v>
-      </c>
-      <c r="E19" t="n">
-        <v>16.55179</v>
-      </c>
-      <c r="F19" t="n">
-        <v>42.2988</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.05131</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.83965</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="C20" t="inlineStr">
+      <c r="C20" t="n">
+        <v>17.24666</v>
+      </c>
+      <c r="D20" t="n">
+        <v>16.40144</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16.96855</v>
+      </c>
+      <c r="F20" t="n">
+        <v>42.58663</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.05033</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.81981</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Dimple</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>via 1</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0.60865</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1.10692</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>via 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.61161</v>
+        <v>0.61537</v>
       </c>
       <c r="D22" t="n">
-        <v>1.12301</v>
+        <v>1.13735</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.59736</v>
+        <v>0.60949</v>
       </c>
       <c r="D23" t="n">
-        <v>1.11119</v>
+        <v>1.12958</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.60914</v>
+        <v>0.60626</v>
       </c>
       <c r="D24" t="n">
-        <v>1.09794</v>
+        <v>1.09129</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.60498</v>
+        <v>0.60601</v>
       </c>
       <c r="D25" t="n">
-        <v>1.09346</v>
+        <v>1.09112</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.60739</v>
+        <v>0.61724</v>
       </c>
       <c r="D26" t="n">
-        <v>1.10608</v>
+        <v>1.10742</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.60683</v>
+        <v>0.60915</v>
       </c>
       <c r="D27" t="n">
-        <v>1.13724</v>
+        <v>1.11531</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.6067900000000001</v>
+        <v>0.5978599999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>1.09957</v>
+        <v>1.10735</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.61273</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1.11459</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>0.61424</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1.12592</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="C30" t="inlineStr">
+      <c r="C30" t="n">
+        <v>0.60177</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.11879</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Rz max</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Rz mean</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Rz min</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>Rz max</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>Ra mean</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Ra Std dev</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>Ra min</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Ra max</t>
         </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>roughness</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>0.75302</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.08058999999999999</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.60762</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.97806</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.00759</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.08928</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.12746</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>roughness</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.7706</v>
+        <v>0.75284</v>
       </c>
       <c r="D32" t="n">
-        <v>0.08139</v>
+        <v>0.08128000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>0.6237</v>
+        <v>0.60882</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9751300000000001</v>
+        <v>0.94981</v>
       </c>
       <c r="G32" t="n">
-        <v>0.11076</v>
+        <v>0.10994</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0076</v>
+        <v>0.00759</v>
       </c>
       <c r="I32" t="n">
-        <v>0.09309000000000001</v>
+        <v>0.09247</v>
       </c>
       <c r="J32" t="n">
-        <v>0.12514</v>
+        <v>0.12738</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.74871</v>
+        <v>0.744</v>
       </c>
       <c r="D33" t="n">
-        <v>0.07894</v>
+        <v>0.08044999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>0.60834</v>
+        <v>0.6021300000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9618</v>
+        <v>0.94693</v>
       </c>
       <c r="G33" t="n">
-        <v>0.10992</v>
+        <v>0.10914</v>
       </c>
       <c r="H33" t="n">
-        <v>0.00761</v>
+        <v>0.00769</v>
       </c>
       <c r="I33" t="n">
-        <v>0.09293999999999999</v>
+        <v>0.09215</v>
       </c>
       <c r="J33" t="n">
-        <v>0.12747</v>
+        <v>0.12572</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.73898</v>
+        <v>0.73922</v>
       </c>
       <c r="D34" t="n">
-        <v>0.08069</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>0.59653</v>
+        <v>0.61159</v>
       </c>
       <c r="F34" t="n">
-        <v>0.95931</v>
+        <v>0.95746</v>
       </c>
       <c r="G34" t="n">
-        <v>0.10647</v>
+        <v>0.10974</v>
       </c>
       <c r="H34" t="n">
-        <v>0.00751</v>
+        <v>0.00775</v>
       </c>
       <c r="I34" t="n">
-        <v>0.09246</v>
+        <v>0.09272</v>
       </c>
       <c r="J34" t="n">
-        <v>0.12571</v>
+        <v>0.1272</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.76528</v>
+        <v>0.7415</v>
       </c>
       <c r="D35" t="n">
-        <v>0.08314000000000001</v>
+        <v>0.08037999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>0.60844</v>
+        <v>0.6045</v>
       </c>
       <c r="F35" t="n">
-        <v>0.93789</v>
+        <v>0.94624</v>
       </c>
       <c r="G35" t="n">
-        <v>0.11041</v>
+        <v>0.10713</v>
       </c>
       <c r="H35" t="n">
-        <v>0.00768</v>
+        <v>0.00752</v>
       </c>
       <c r="I35" t="n">
-        <v>0.09089</v>
+        <v>0.09275</v>
       </c>
       <c r="J35" t="n">
-        <v>0.12601</v>
+        <v>0.12663</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.74969</v>
+        <v>0.74169</v>
       </c>
       <c r="D36" t="n">
-        <v>0.08096</v>
+        <v>0.08099000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>0.6058</v>
+        <v>0.60236</v>
       </c>
       <c r="F36" t="n">
-        <v>0.96024</v>
+        <v>0.95943</v>
       </c>
       <c r="G36" t="n">
-        <v>0.10969</v>
+        <v>0.10914</v>
       </c>
       <c r="H36" t="n">
-        <v>0.00772</v>
+        <v>0.00764</v>
       </c>
       <c r="I36" t="n">
-        <v>0.09202</v>
+        <v>0.09392</v>
       </c>
       <c r="J36" t="n">
-        <v>0.12758</v>
+        <v>0.12525</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.73972</v>
+        <v>0.7489400000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>0.08212</v>
+        <v>0.08215</v>
       </c>
       <c r="E37" t="n">
-        <v>0.60987</v>
+        <v>0.60778</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9838</v>
+        <v>0.98209</v>
       </c>
       <c r="G37" t="n">
-        <v>0.11009</v>
+        <v>0.10953</v>
       </c>
       <c r="H37" t="n">
-        <v>0.00743</v>
+        <v>0.00755</v>
       </c>
       <c r="I37" t="n">
-        <v>0.09327000000000001</v>
+        <v>0.09442</v>
       </c>
       <c r="J37" t="n">
-        <v>0.1253</v>
+        <v>0.12714</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.73273</v>
+        <v>0.76103</v>
       </c>
       <c r="D38" t="n">
-        <v>0.08029</v>
+        <v>0.08114</v>
       </c>
       <c r="E38" t="n">
-        <v>0.60738</v>
+        <v>0.61046</v>
       </c>
       <c r="F38" t="n">
-        <v>0.96528</v>
+        <v>0.96952</v>
       </c>
       <c r="G38" t="n">
-        <v>0.10955</v>
+        <v>0.1103</v>
       </c>
       <c r="H38" t="n">
         <v>0.00753</v>
       </c>
       <c r="I38" t="n">
-        <v>0.09264</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>0.12776</v>
+        <v>0.12631</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7608</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.08144999999999999</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.60114</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.93424</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.10889</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.00739</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.09271</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.12599</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C39" t="n">
-        <v>0.74722</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.08129</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.613</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.9764</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.11316</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.00754</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0.09107</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0.1244</v>
+      <c r="C40" t="n">
+        <v>0.74773</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.08037999999999999</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.6049600000000001</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.97371</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.11016</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.00763</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.09208</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.12629</v>
       </c>
     </row>
   </sheetData>
